--- a/output/pdf_financials_xlsx/HSLV.xlsx
+++ b/output/pdf_financials_xlsx/HSLV.xlsx
@@ -3554,7 +3554,7 @@
         <v>1.385293</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.724026</v>
       </c>
     </row>
     <row r="93">
@@ -4419,16 +4419,16 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.50532</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.039961</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.285257</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-1.224073</v>
       </c>
     </row>
     <row r="119">
@@ -6106,7 +6106,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10444,7 +10448,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -12012,7 +12020,11 @@
           <t>Deferred exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -12670,7 +12682,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HSLV.xlsx
+++ b/output/pdf_financials_xlsx/HSLV.xlsx
@@ -787,13 +787,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000864</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.015276</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019353</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1332,13 +1332,13 @@
         <v>-0.434718</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.578788</v>
+        <v>-1.579652</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.718623</v>
+        <v>-0.733899</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.549525</v>
+        <v>-5.568878</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         <v>-0.434718</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.571528</v>
+        <v>-1.572392</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.708643</v>
+        <v>-0.723919</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.539112</v>
+        <v>-5.558465</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.423173</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.7438129999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.50284</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.968174</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.229702</v>
@@ -1627,16 +1627,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.423173</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.7438129999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.50284</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.968174</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.229702</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.5175</v>
+        <v>0.01466</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.990854</v>
+        <v>0.02268</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.014268</v>
@@ -5432,7 +5432,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -6416,7 +6420,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7510,7 +7514,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -8032,7 +8036,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -13842,7 +13846,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">

--- a/output/pdf_financials_xlsx/HSLV.xlsx
+++ b/output/pdf_financials_xlsx/HSLV.xlsx
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.007774</v>
       </c>
     </row>
     <row r="113">
@@ -10622,7 +10622,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HSLV.xlsx
+++ b/output/pdf_financials_xlsx/HSLV.xlsx
@@ -622,13 +622,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.101128</v>
+        <v>0.106917</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.078615</v>
+        <v>0.116021</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.020951</v>
+        <v>0.10763</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -3742,10 +3742,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.000353</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.032689</v>
@@ -3777,10 +3775,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -3812,10 +3808,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -3847,10 +3841,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -3882,10 +3874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -3917,10 +3907,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.000352</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.013947</v>
@@ -3952,10 +3940,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -3987,10 +3973,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.000352</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.013947</v>
@@ -4022,10 +4006,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -4057,10 +4039,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -4092,10 +4072,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -4127,10 +4105,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -4148,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.008237</v>
       </c>
     </row>
     <row r="111">
@@ -4162,10 +4138,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -4177,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001876</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031543</v>
       </c>
     </row>
     <row r="112">
@@ -4197,10 +4171,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -4232,10 +4204,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -4267,10 +4237,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -4302,10 +4270,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -4337,10 +4303,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -4372,10 +4336,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -4407,10 +4369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -4442,10 +4402,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>0</v>
@@ -4479,10 +4437,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -4514,10 +4470,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -4549,10 +4503,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -4584,10 +4536,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -4619,10 +4569,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -4654,10 +4602,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -4689,10 +4635,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -4771,10 +4715,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -4806,10 +4748,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>1e-06</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>0.4428</v>
@@ -4886,10 +4826,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -4921,10 +4859,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.423173</v>
@@ -4995,10 +4931,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -5010,13 +4944,13 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001876</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031543</v>
       </c>
     </row>
     <row r="135">
@@ -5030,10 +4964,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.019627</v>
@@ -5047,7 +4979,7 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.243447</v>
+        <v>-0.245323</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -5071,7 +5003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9602,7 +9534,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -10566,7 +10502,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -11972,7 +11912,11 @@
           <t>Purchases of equipment 3</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -12634,7 +12578,11 @@
           <t>Purchases of equipment 4</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -13239,15 +13187,17 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>For the Period October 19, 2016 (Inception) to September</t>
+          <t>Net loss and comprehensive loss for the period (32,689)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>3e-05</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.002017</v>
+        <v>-0.000353</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -13283,13 +13233,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>For the years ended September 30, 2023 and September</t>
+          <t>Sales tax receivables (885)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -13318,11 +13272,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="K147" s="5" t="n">
-        <v>3e-05</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -13333,22 +13291,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
+          <t>Increase in accounts payable and accrued liabilities 13,947</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13356,10 +13314,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F148" s="5" t="n">
+        <v>0.000352</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -13371,14 +13327,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="5" t="n">
-        <v>0.009825</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>0.045994</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0.015238</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -13389,22 +13351,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Cash flows used in operating activities (19,627)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13412,10 +13374,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F149" s="5" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -13427,14 +13387,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="5" t="n">
-        <v>0.092055</v>
-      </c>
-      <c r="J149" s="5" t="n">
-        <v>0.05825</v>
-      </c>
-      <c r="K149" s="5" t="n">
-        <v>0.001119</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -13445,33 +13411,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Depreciation 3</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Proceeds from incorporator shares -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F150" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -13488,11 +13448,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J150" s="5" t="n">
-        <v>0.009979999999999999</v>
-      </c>
-      <c r="K150" s="5" t="n">
-        <v>0.010413</v>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -13503,22 +13467,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Proceeds from private placement 442,800</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13541,14 +13505,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="5" t="n">
-        <v>0.07341399999999999</v>
-      </c>
-      <c r="J151" s="5" t="n">
-        <v>-0.242118</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>0.063738</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -13559,29 +13529,31 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Office expenses</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Cash flows provided by financing activities 442,800</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -13593,14 +13565,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="5" t="n">
-        <v>0.005789</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>0.037406</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>0.08667900000000001</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -13611,22 +13589,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Professional fees 6</t>
+          <t>Increase in cash 423,173</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13654,11 +13632,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J153" s="5" t="n">
-        <v>0.404029</v>
-      </c>
-      <c r="K153" s="5" t="n">
-        <v>0.503259</v>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -13669,17 +13651,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share-based payments 5,6</t>
+          <t>Cash, beginning -</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -13708,11 +13690,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J154" s="5" t="n">
-        <v>0.399993</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.225314</v>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -13723,24 +13709,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cash, ending 423,173</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -13761,14 +13743,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="5" t="n">
-        <v>0.009072999999999999</v>
-      </c>
-      <c r="J155" s="5" t="n">
-        <v>0.020365</v>
-      </c>
-      <c r="K155" s="5" t="n">
-        <v>0.019832</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -13779,33 +13767,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss from operating expenses</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>For the Period October 19, 2016 (Inception) to September</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.002017</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -13817,14 +13793,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="5" t="n">
-        <v>0.477904</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>0.733899</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0.925592</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -13838,21 +13820,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>For the years ended September 30, 2023 and September</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -13873,14 +13847,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>0.000864</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0.015276</v>
+        <v>0.002022</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>0.019353</v>
+        <v>3e-05</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -13901,10 +13877,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Recovery of accounts payable</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -13925,18 +13905,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I158" s="5" t="n">
+        <v>0.009825</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>0.045994</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>0.042167</v>
+        <v>0.015238</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -13957,10 +13933,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Write off of receivable</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -13981,18 +13961,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="5" t="n">
+        <v>0.092055</v>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>0.05825</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>-0.076794</v>
+        <v>0.001119</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -14013,10 +13989,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Write-off of mineral property interests 4</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Depreciation 3</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -14042,13 +14022,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J160" s="5" t="n">
+        <v>0.009979999999999999</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>-4.608659</v>
+        <v>0.010413</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -14069,12 +14047,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14098,13 +14076,13 @@
         </is>
       </c>
       <c r="I161" s="5" t="n">
-        <v>-1.578788</v>
+        <v>0.07341399999999999</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>-0.718623</v>
+        <v>-0.242118</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>-5.549525</v>
+        <v>0.063738</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -14125,10 +14103,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Exchange differences on translating foreign operations</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Office expenses</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -14150,13 +14132,13 @@
         </is>
       </c>
       <c r="I162" s="5" t="n">
-        <v>-0.216749</v>
+        <v>0.005789</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>-0.018054</v>
+        <v>0.037406</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>0.233537</v>
+        <v>0.08667900000000001</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -14177,12 +14159,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Professional fees 6</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14205,14 +14187,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="5" t="n">
-        <v>-1.795537</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J163" s="5" t="n">
-        <v>-0.736677</v>
+        <v>0.404029</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>-5.315988</v>
+        <v>0.503259</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -14233,7 +14217,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Owners of the Company</t>
+          <t>Share-based payments 5,6</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -14257,14 +14241,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="5" t="n">
-        <v>-1.578788</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="5" t="n">
-        <v>-0.718623</v>
+        <v>0.399993</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>-5.549525</v>
+        <v>0.225314</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -14285,10 +14271,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Owners of the Company - Foreign exchange translation</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -14310,13 +14300,13 @@
         </is>
       </c>
       <c r="I165" s="5" t="n">
-        <v>-0.216749</v>
+        <v>0.009072999999999999</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>-0.018054</v>
+        <v>0.020365</v>
       </c>
       <c r="K165" s="5" t="n">
-        <v>0.233537</v>
+        <v>0.019832</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -14337,7 +14327,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Loss from operating expenses</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -14366,13 +14356,13 @@
         </is>
       </c>
       <c r="I166" s="5" t="n">
-        <v>1.795537</v>
+        <v>0.477904</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>0.736677</v>
+        <v>0.733899</v>
       </c>
       <c r="K166" s="5" t="n">
-        <v>5.315988</v>
+        <v>0.925592</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -14388,17 +14378,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>- basic #</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14422,13 +14412,13 @@
         </is>
       </c>
       <c r="I167" s="5" t="n">
-        <v>41.340182</v>
+        <v>0.000864</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>30.278734</v>
+        <v>0.015276</v>
       </c>
       <c r="K167" s="5" t="n">
-        <v>30.423174</v>
+        <v>0.019353</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -14444,19 +14434,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>- diluted #</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Recovery of accounts payable</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -14477,14 +14463,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="5" t="n">
-        <v>41.340182</v>
-      </c>
-      <c r="J168" s="5" t="n">
-        <v>30.278734</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>30.423174</v>
+        <v>0.042167</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -14500,12 +14490,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Basic loss per share $</t>
+          <t>Write off of receivable</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -14529,14 +14519,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="J169" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>-0.076794</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -14552,12 +14546,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Diluted loss per share $</t>
+          <t>Write-off of mineral property interests 4</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -14581,14 +14575,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="J170" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>-4.608659</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -14602,13 +14600,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>For the year ended September 30, 2022 and the nine month period ended September</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -14630,15 +14636,13 @@
         </is>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0.002021</v>
+        <v>-1.578788</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.718623</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>-5.549525</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -14659,14 +14663,10 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Depreciation 4</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Exchange differences on translating foreign operations</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -14688,15 +14688,13 @@
         </is>
       </c>
       <c r="I172" s="5" t="n">
-        <v>0.00726</v>
+        <v>-0.216749</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>0.009979999999999999</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.018054</v>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>0.233537</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -14717,12 +14715,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Professional fees 7</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -14746,15 +14744,13 @@
         </is>
       </c>
       <c r="I173" s="5" t="n">
-        <v>0.280488</v>
+        <v>-1.795537</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>0.404029</v>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.736677</v>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>-5.315988</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -14775,7 +14771,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Share-based payments (1) 6,7</t>
+          <t>Owners of the Company</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -14799,18 +14795,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I174" s="5" t="n">
+        <v>-1.578788</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>0.399993</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.718623</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>-5.549525</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -14831,7 +14823,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Listing expense</t>
+          <t>Owners of the Company - Foreign exchange translation</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -14856,17 +14848,13 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>-0.86097</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.216749</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>-0.018054</v>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.233537</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -14887,10 +14875,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Non-recoverable taxes</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -14912,17 +14904,13 @@
         </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>-0.010778</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.795537</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0.736677</v>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>5.315988</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -14938,15 +14926,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Write-off of mineral property interests 5</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>- basic #</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -14968,17 +14960,13 @@
         </is>
       </c>
       <c r="I177" s="5" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>41.340182</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>30.278734</v>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>30.423174</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -14992,13 +14980,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>September 30, 2019 September</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>- diluted #</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -15009,26 +15005,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G178" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="H178" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>41.340182</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>30.278734</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>30.423174</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -15044,12 +15038,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Basic loss per share $</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -15063,26 +15057,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" s="5" t="n">
-        <v>0.0063</v>
-      </c>
-      <c r="H179" s="5" t="n">
-        <v>0.028391</v>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -15098,19 +15090,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Consulting (Note 10)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -15121,26 +15109,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G180" s="5" t="n">
-        <v>0.01165</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>0.119395</v>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -15154,21 +15140,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>For the year ended September 30, 2022 and the nine month period ended September</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -15179,21 +15157,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G181" s="5" t="n">
-        <v>0.014739</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0.068546</v>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -15214,15 +15192,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Interest expense                                                            2,370                            ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Interest expense                                                            2,370                            ‐ total</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Depreciation 4</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -15233,21 +15215,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G182" s="5" t="n">
-        <v>-0.032689</v>
-      </c>
-      <c r="H182" s="5" t="n">
-        <v>-0.218702</v>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>0.00726</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>0.009979999999999999</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -15268,17 +15250,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
+          <t>Professional fees 7</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15291,21 +15273,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" s="5" t="n">
-        <v>-0.032689</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>-0.434718</v>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>0.280488</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>0.404029</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -15326,19 +15308,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based payments (1) 6,7</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -15349,21 +15327,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G184" s="5" t="n">
-        <v>-7.18e-06</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J184" s="5" t="n">
+        <v>0.399993</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -15384,19 +15364,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 4)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -15407,16 +15383,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G185" s="5" t="n">
-        <v>0.004553</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>7.154298</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>-0.86097</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -15442,12 +15420,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Number    Amount   Warrants     Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2017 10 1</t>
+          <t>Non-recoverable taxes</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -15461,16 +15439,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G186" s="5" t="n">
-        <v>-0.000352</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>-0.000353</v>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>-0.010778</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -15496,19 +15476,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss ‐ ‐ ‐</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of mineral property interests 5</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -15519,16 +15495,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" s="5" t="n">
-        <v>-0.032689</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>-0.032689</v>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>-0.23</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -15552,14 +15530,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
-        </is>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2018 151,054 11,000 442,800</t>
+          <t>September 30, 2019 September</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -15574,10 +15548,10 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.420758</v>
+        <v>0.002018</v>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-0.033042</v>
+        <v>3e-05</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15608,12 +15582,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2019 11,035,054 1,332,600 ‐</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -15628,10 +15602,10 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.8648400000000001</v>
+        <v>0.0063</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>-0.46776</v>
+        <v>0.028391</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15662,32 +15636,34 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>(Blue Aqua Holdings Ltd.)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>For the year ended September</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Consulting (Note 10)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.01165</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0.119395</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15723,27 +15699,29 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Administration 6,300</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>0.000353</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.014739</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0.068546</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15774,12 +15752,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Interest expense                                                            2,370                            ‐</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Audit 7,650</t>
+          <t>Interest expense                                                            2,370                            ‐ total</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -15793,15 +15771,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G192" s="5" t="n">
+        <v>-0.032689</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>-0.218702</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15832,17 +15806,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Management fees (Note 9) 11,650</t>
+          <t>Net and comprehensive loss</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -15855,15 +15829,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G193" s="5" t="n">
+        <v>-0.032689</v>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>-0.434718</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15894,17 +15864,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Professional fees 7,089</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -15917,15 +15887,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G194" s="5" t="n">
+        <v>-7.18e-06</v>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15956,32 +15922,34 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss on foreign currency                                                      (17,491)                            ‐</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period (32,689)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding (Note 4)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F195" s="5" t="n">
-        <v>-0.000353</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.004553</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>7.154298</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -16012,12 +15980,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number    Amount   Warrants     Deficit        Total</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Notes 4 and 10) $ (0.72) $</t>
+          <t>Balance, September 30, 2017 10 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -16026,18 +15994,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F196" s="5" t="n">
-        <v>-3.53e-05</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>-0.000352</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>-0.000353</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16068,17 +16034,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Notes 4 and 10) 45,530</t>
+          <t>Net and comprehensive loss ‐ ‐ ‐</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -16086,18 +16052,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>-0.032689</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>-0.032689</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -16128,12 +16092,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>(Date of Incorporation) – Issuance to</t>
+          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Incorporator (Note 4) 100 1 -</t>
+          <t>Balance, September 30, 2018 151,054 11,000 442,800</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -16142,18 +16106,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.420758</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>-0.033042</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -16184,36 +16146,30 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>(Date of Incorporation) – Issuance to</t>
+          <t>Incorporator shares cancelled                          (10)            (1)               ‐                ‐            (1)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Net loss for the period - - (353)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, September 30, 2019 11,035,054 1,332,600 ‐</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F199" s="5" t="n">
-        <v>-0.000353</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.8648400000000001</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>-0.46776</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -16244,12 +16200,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>(Date of Incorporation) – Issuance to</t>
+          <t>(Blue Aqua Holdings Ltd.)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2017 100 1 (353)</t>
+          <t>For the year ended September</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -16259,7 +16215,7 @@
         </is>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.000352</v>
+        <v>3e-05</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -16300,12 +16256,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Shares issued pursuant to plan of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Shares issued pursuant to plan of arrangement (Notes 4 and 6) 1,010,549 1,000 - -</t>
+          <t>Administration 6,300</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -16315,7 +16271,7 @@
         </is>
       </c>
       <c r="F201" s="5" t="n">
-        <v>0.001</v>
+        <v>0.000353</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -16356,12 +16312,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Shares issued pursuant to plan of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Shares issued for services (Notes 4 and 9) 500,000 10,000 - -</t>
+          <t>Audit 7,650</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -16370,8 +16326,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" s="5" t="n">
-        <v>0.01</v>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -16412,22 +16370,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Shares issued pursuant to plan of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Incorporator shares cancelled (100) (1) - -</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Management fees (Note 9) 11,650</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F203" s="5" t="n">
-        <v>-1e-06</v>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -16468,22 +16432,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Warrants Issued for private placement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>(Note 4) - - 442,800 -</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Professional fees 7,089</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F204" s="5" t="n">
-        <v>0.4428</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -16524,12 +16494,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Warrants Issued for private placement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - (32,689)</t>
+          <t>Net loss and comprehensive loss for the period (32,689)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -16539,7 +16509,7 @@
         </is>
       </c>
       <c r="F205" s="5" t="n">
-        <v>-0.032689</v>
+        <v>-0.000353</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -16580,12 +16550,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Warrants Issued for private placement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2018 1,510,549 11,000 442,800 (33,042)</t>
+          <t>Basic and diluted loss per common share (Notes 4 and 10) $ (0.72) $</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -16595,7 +16565,7 @@
         </is>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.420758</v>
+        <v>-3.53e-05</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -16634,18 +16604,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>For the Period October 19, 2016 (Inception) to September</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" s="5" t="n">
-        <v>3e-05</v>
+          <t>Weighted average number of common shares outstanding (Notes 4 and 10) 45,530</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F207" s="5" t="n">
-        <v>0.002017</v>
+        <v>1e-05</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -16686,20 +16666,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>(Date of Incorporation) – Issuance to</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Balance, October</t>
+          <t>Incorporator (Note 4) 100 1 -</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" s="5" t="n">
-        <v>1.9e-05</v>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.002016</v>
+        <v>1e-06</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -16745,17 +16727,21 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Incorporator - $0.01 100 1</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Net loss for the period - - (353)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F209" s="5" t="n">
-        <v>1e-06</v>
+        <v>-0.000353</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -16801,19 +16787,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Net Loss for the period — —</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="n">
-        <v>-0.000353</v>
+          <t>Balance, September 30, 2017 100 1 (353)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.000353</v>
+        <v>-0.000352</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -16854,47 +16838,601 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
+          <t>Shares issued pursuant to plan of</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Shares issued pursuant to plan of arrangement (Notes 4 and 6) 1,010,549 1,000 - -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Shares issued pursuant to plan of</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Shares issued for services (Notes 4 and 9) 500,000 10,000 - -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Shares issued pursuant to plan of</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Incorporator shares cancelled (100) (1) - -</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Warrants Issued for private placement</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>(Note 4) - - 442,800 -</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Warrants Issued for private placement</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - (32,689)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>-0.032689</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Warrants Issued for private placement</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Balance, September 30, 2018 1,510,549 11,000 442,800 (33,042)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.420758</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>For the Period October 19, 2016 (Inception) to September</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Balance, October</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>1.9e-05</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
           <t>(Date of Incorporation) – Issuance to</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Incorporator - $0.01 100 1</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>(Date of Incorporation) – Issuance to</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Net Loss for the period — —</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>-0.000353</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>-0.000353</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>(Date of Incorporation) – Issuance to</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Balance, September 30, 2017 100 1</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" s="5" t="n">
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
         <v>-0.000353</v>
       </c>
-      <c r="F211" s="5" t="n">
+      <c r="F221" s="5" t="n">
         <v>-0.000352</v>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
